--- a/src/equipos/equipos.xlsx
+++ b/src/equipos/equipos.xlsx
@@ -1,93 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\TeamComunicaciones\automatizadorteam\src\equipos\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEC8740-1F8C-4D26-8EB5-BF6AB3FAA6B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="2175" yWindow="3960" windowWidth="13005" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Iccid</t>
-  </si>
-  <si>
-    <t>Imei</t>
-  </si>
-  <si>
-    <t>Cedula vendedor</t>
-  </si>
-  <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Preactivado</t>
-  </si>
-  <si>
-    <t>Mensaje</t>
-  </si>
-  <si>
-    <t>Msisdn2</t>
-  </si>
-  <si>
-    <t>ICC_ID_Identificacion_Tarjeta_de_Circuito_Integrada</t>
-  </si>
-  <si>
-    <t>IMEI_Identificacion_Internacional_del_Equipo_Movil</t>
-  </si>
-  <si>
-    <t>Validacion_Tecnologia</t>
-  </si>
-  <si>
-    <t>Validacion_Kit_Prepago</t>
-  </si>
-  <si>
-    <t>Validacion_Region_ICCID_Distribuidor</t>
-  </si>
-  <si>
-    <t>Validacion_Equipo</t>
-  </si>
-  <si>
-    <t>Validacion_Lista</t>
-  </si>
-  <si>
-    <t>Codigo_distribuidor</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -102,43 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -426,63 +420,2660 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Iccid</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Imei</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cedula vendedor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Mensaje</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>ICC_ID_Identificacion_Tarjeta_de_Circuito_Integrada</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>IMEI_Identificacion_Internacional_del_Equipo_Movil</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Validacion_Tecnologia</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Validacion_Kit_Prepago</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Validacion_Region_ICCID_Distribuidor</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Validacion_Equipo</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Validacion_Lista</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Codigo_distribuidor</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474848</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 866567079343001</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3227803460</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474849</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688079277449</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3227848806</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474850</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688079848843</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3227896998</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474851</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688073778285</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D5" t="n">
+        <v>3227887525</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474852</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688071558986</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3227907681</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474853</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688073852247</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3227896602</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474854</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 863391072691925</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3227901627</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474857</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688073757081</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3227935124</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474860</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 863391073203100</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3227864194</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474869</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688071867965</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3228003148</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474870</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688073820004</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3227956733</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474871</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 860688073882467</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3227970540</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474872</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 867469072921728</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3228010403</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474874</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 863391072081986</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3227940647</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474876</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600927919</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3227943151</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474878</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600928263</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3227941926</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474882</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600928438</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3227945865</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474890</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600963740</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3227962058</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474891</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600964359</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3227967044</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474895</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600966289</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3227973292</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474898</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600967626</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3227975858</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474913</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600968079</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3227975874</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474915</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600969283</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3227977129</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474921</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600969705</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3227979628</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474923</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600971404</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3227983396</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474925</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600971594</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3227987106</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474927</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600971974</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3228017604</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474929</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600973038</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3227997370</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474930</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600973053</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3228007386</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474932</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600973772</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3227943424</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474939</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600974200</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3227954703</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474942</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600975140</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3227978424</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474943</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600983268</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>3227962213</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474944</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600985040</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3227964733</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474945</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600985388</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>3227968490</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474946</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600922787</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>3227970987</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474947</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600942074</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474950</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600943460</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474951</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600952560</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474952</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600958526</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474954</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600984621</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474956</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601056437</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474957</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600939385</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474958</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600964177</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474959</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600966149</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474964</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600968269</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474977</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270600974671</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474979</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601875836</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474981</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601860507</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474985</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601755699</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474986</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270602057533</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474995</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270602058374</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404474999</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601905617</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475003</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270602052955</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475008</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601541040</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475010</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601804216</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475015</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601874235</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475016</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601875067</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475018</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601875224</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475020</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601884473</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475021</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601885975</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475025</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601886197</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475026</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601886957</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475028</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601886965</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475031</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601886981</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475036</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887070</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475038</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887195</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475041</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887278</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475043</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887427</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475044</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887435</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475049</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887500</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475055</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887534</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475058</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887583</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475070</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601887617</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475071</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601905831</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475072</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601905922</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475077</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601906854</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475078</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601907522</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475080</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601907944</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475084</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601908439</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475087</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601890215</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475088</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601895008</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475089</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601895396</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475090</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601895594</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475094</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601896360</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475095</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601896584</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475097</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601896733</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475101</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601896741</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475102</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601896766</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475104</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601896774</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475105</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601897103</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475111</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601897160</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475115</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601897525</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475117</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601897582</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475118</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601897640</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475122</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601898051</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475137</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601898069</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475141</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601898135</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475142</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601898192</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 57101602404475143</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 353270601898234</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1036962271</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
